--- a/output/pdf_financials_xlsx/PGIC.xlsx
+++ b/output/pdf_financials_xlsx/PGIC.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/PGIC.xlsx
+++ b/output/pdf_financials_xlsx/PGIC.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.324074</v>
+        <v>3.400731</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.443021</v>
+        <v>2.496188</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.989798</v>
+        <v>1.892878</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.669284</v>
+        <v>1.450686</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.370274</v>
+        <v>0.789144</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.360687</v>
+        <v>0.826986</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8.360573</v>
+        <v>7.283916</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.338307</v>
+        <v>-1.391474</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.974211</v>
+        <v>0.071131</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.148406</v>
+        <v>0.367004</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.609592</v>
+        <v>0.190722</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.342988</v>
+        <v>-0.123311</v>
       </c>
     </row>
     <row r="12">
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.529457</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.038736</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.044966</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.642081</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.265373</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.536357</v>
       </c>
     </row>
     <row r="35">
@@ -1341,22 +1341,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.529457</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.038736</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.044966</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.642081</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.265373</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.536357</v>
       </c>
     </row>
     <row r="37">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E359" s="5" t="n">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E452" s="5" t="n">

--- a/output/pdf_financials_xlsx/PGIC.xlsx
+++ b/output/pdf_financials_xlsx/PGIC.xlsx
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.324074</v>
+        <v>2.341391</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.443021</v>
+        <v>1.462652</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.989798</v>
+        <v>1.010373</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.669284</v>
+        <v>0.689859</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.370274</v>
+        <v>0.39022</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.360687</v>
+        <v>0.379587</v>
       </c>
     </row>
     <row r="8">
@@ -19190,7 +19190,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E354" s="5" t="n">
         <v>0.017317</v>
       </c>
@@ -24388,7 +24392,11 @@
           <t>Distributions to Preferred shares</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E476" s="5" t="n">
         <v>-6.811437</v>
       </c>
